--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.37</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>3.46</v>
+        <v>5.33</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>4.04</v>
       </c>
       <c r="M19" t="n">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.04</v>
+        <v>2.36</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.46</v>
       </c>
       <c r="N21" t="n">
-        <v>1.93</v>
+        <v>3.31</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.37</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB12" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>3.59</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.62</v>
+        <v>2.36</v>
       </c>
       <c r="M20" t="n">
-        <v>4.37</v>
+        <v>3.46</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>3.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.36</v>
+        <v>4.04</v>
       </c>
       <c r="M21" t="n">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.31</v>
+        <v>1.93</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>3.59</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="M17" t="n">
-        <v>5.33</v>
+        <v>3.46</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>3.31</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="N21" t="n">
-        <v>1.93</v>
+        <v>1.37</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>3.59</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>3.59</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>4.04</v>
       </c>
       <c r="M17" t="n">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>1.93</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.62</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>4.37</v>
+        <v>5.33</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.04</v>
+        <v>4.62</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="M21" t="n">
-        <v>5.33</v>
+        <v>3.46</v>
       </c>
       <c r="N21" t="n">
-        <v>1.37</v>
+        <v>3.31</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.37</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.36</v>
+        <v>4.04</v>
       </c>
       <c r="M21" t="n">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.31</v>
+        <v>1.93</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.37</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB12" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.59</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>3.59</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.62</v>
+        <v>4.04</v>
       </c>
       <c r="M19" t="n">
-        <v>4.37</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.04</v>
+        <v>4.62</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="N21" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.59</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.04</v>
+        <v>4.62</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.62</v>
+        <v>4.04</v>
       </c>
       <c r="M21" t="n">
-        <v>4.37</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.37</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="M18" t="n">
-        <v>5.33</v>
+        <v>3.46</v>
       </c>
       <c r="N18" t="n">
-        <v>1.37</v>
+        <v>3.31</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>3.46</v>
+        <v>5.33</v>
       </c>
       <c r="N20" t="n">
-        <v>3.31</v>
+        <v>1.37</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.37</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB12" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.36</v>
+        <v>4.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3.46</v>
+        <v>4.37</v>
       </c>
       <c r="N18" t="n">
-        <v>3.31</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="M20" t="n">
-        <v>5.33</v>
+        <v>3.46</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>3.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.62</v>
+        <v>2.36</v>
       </c>
       <c r="M18" t="n">
-        <v>4.37</v>
+        <v>3.46</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>3.31</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.04</v>
+        <v>4.62</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="N21" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.04</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="N17" t="n">
-        <v>1.93</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>4.04</v>
       </c>
       <c r="M19" t="n">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -787,19 +787,19 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.37</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="M17" t="n">
-        <v>5.33</v>
+        <v>3.46</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>3.31</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>3.46</v>
+        <v>5.33</v>
       </c>
       <c r="N20" t="n">
-        <v>3.31</v>
+        <v>1.37</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8.5</v>
+        <v>10.46</v>
       </c>
       <c r="M2" t="n">
         <v>5.25</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="O2" t="n">
         <v>8.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.13</v>
@@ -701,25 +701,25 @@
         <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
         <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AC2" t="n">
         <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
         <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
         <v>1.06</v>
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46071.45833333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.87</v>
+        <v>1.79</v>
       </c>
       <c r="M6" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>5.18</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.79</v>
+        <v>2.87</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="N7" t="n">
-        <v>5.18</v>
+        <v>2.69</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.04</v>
+        <v>2.36</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.46</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>3.31</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>4.04</v>
       </c>
       <c r="M20" t="n">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>1.93</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10.46</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8.5</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.58</v>
-      </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="P3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>2.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -915,10 +915,10 @@
         <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T4" t="n">
         <v>2.43</v>
@@ -927,13 +927,13 @@
         <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46071.58333333334</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N6" t="n">
-        <v>5.18</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="N9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46071.61458333334</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="M10" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O10" t="n">
         <v>4</v>
@@ -1632,52 +1632,52 @@
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
         <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF10" t="n">
         <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46071.625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.22</v>
+        <v>1.76</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.37</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB12" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="M18" t="n">
-        <v>5.33</v>
+        <v>3.46</v>
       </c>
       <c r="N18" t="n">
-        <v>1.37</v>
+        <v>3.31</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>3.46</v>
+        <v>5.33</v>
       </c>
       <c r="N19" t="n">
-        <v>3.31</v>
+        <v>1.37</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.04</v>
+        <v>4.62</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="N20" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="P2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>7.7</v>
+        <v>4.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>2.46</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>8.5</v>
+        <v>3.15</v>
       </c>
       <c r="P3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.58</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>4.45</v>
+        <v>7.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>3.14</v>
       </c>
       <c r="M6" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>3.94</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.96</v>
+        <v>3.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.77</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1495,7 +1495,7 @@
         <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.87</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
         <v>1.44</v>
@@ -1507,16 +1507,16 @@
         <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
         <v>1.57</v>
@@ -1534,19 +1534,19 @@
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
         <v>2.34</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
         <v>1.83</v>
@@ -1558,7 +1558,7 @@
         <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46071.61458333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N11" t="n">
-        <v>1.76</v>
+        <v>4.22</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.37</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4.22</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.04</v>
+        <v>4.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="T17" t="n">
         <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>5.33</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>3.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>3.24</v>
       </c>
       <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.33</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.62</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>4.37</v>
+        <v>5.33</v>
       </c>
       <c r="N20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1.75</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.25</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S6" t="n">
         <v>2.17</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.07</v>
-      </c>
       <c r="T6" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.85</v>
+        <v>3.14</v>
       </c>
       <c r="M7" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>3.94</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.96</v>
+        <v>3.68</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.77</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="N9" t="n">
         <v>1.44</v>
@@ -1528,19 +1528,19 @@
         <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
         <v>2.49</v>
@@ -1558,7 +1558,7 @@
         <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46071.61458333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4.22</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>3.59</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>3.59</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.75</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>5.33</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.24</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.03</v>
+        <v>3.42</v>
       </c>
       <c r="T19" t="n">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,552 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>5.33</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>3.08</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>3.24</v>
       </c>
       <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.33</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46071</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Club Brugge</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI21" s="3" t="n">
-        <v>46071.70833333334</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46071</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Tivoli Gardens</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>46071.8125</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46071</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3" t="n">
-        <v>46071.875</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>46071</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Harbour View</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Montego Bay United</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3" t="n">
-        <v>46071.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8.5</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.58</v>
-      </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>4.45</v>
+        <v>7.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="P3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>7.7</v>
+        <v>4.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>2.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.17</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.07</v>
-      </c>
       <c r="T7" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>7.07</v>
       </c>
       <c r="M9" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="N9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>6.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="M18" t="n">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="U18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2804,7 +2804,7 @@
         <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
         <v>2.8</v>
@@ -2819,13 +2819,13 @@
         <v>3.24</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
         <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="U20" t="n">
         <v>1.44</v>
@@ -2837,22 +2837,22 @@
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD20" t="n">
         <v>1.3</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="P2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>7.7</v>
+        <v>4.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>2.46</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>8.5</v>
+        <v>3.15</v>
       </c>
       <c r="P3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.58</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>4.45</v>
+        <v>7.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.46</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.8</v>
+        <v>3.53</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1260,67 +1260,67 @@
         <v>2.88</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.96</v>
+        <v>5.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
         <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
         <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AD7" t="n">
         <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="N8" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="T8" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.07</v>
+        <v>7.25</v>
       </c>
       <c r="M9" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O9" t="n">
         <v>6.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.8</v>
@@ -1519,10 +1519,10 @@
         <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V9" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.12</v>
@@ -1540,13 +1540,13 @@
         <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC9" t="n">
         <v>2.49</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE9" t="n">
         <v>1.83</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.59</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>3.59</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>5.33</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T17" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="W17" t="n">
         <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.7</v>
+        <v>4.54</v>
       </c>
       <c r="M18" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
         <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.75</v>
+        <v>2.39</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.45</v>
       </c>
-      <c r="M20" t="n">
+      <c r="Q20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.3</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.58</v>
+        <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>4.45</v>
+        <v>6.75</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.46</v>
+        <v>1.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2.98</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O3" t="n">
-        <v>3.15</v>
+        <v>8.5</v>
       </c>
       <c r="P3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>7.7</v>
+        <v>4.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -906,64 +906,64 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>6.95</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46071.45833333334</v>
@@ -1055,7 +1055,7 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
         <v>3.9</v>
@@ -1067,19 +1067,19 @@
         <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD5" t="n">
         <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
         <v>1.43</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.53</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>3.86</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
         <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.75</v>
+        <v>5.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>3.53</v>
       </c>
       <c r="M8" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="O8" t="n">
-        <v>3.86</v>
+        <v>4.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="T8" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
         <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
         <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.54</v>
+        <v>2.39</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.65</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.39</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.3</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.08</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>6.55</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>4.54</v>
       </c>
       <c r="M20" t="n">
-        <v>5.33</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>9.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.82</v>
+        <v>3.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>6.75</v>
+        <v>4.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>5.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.98</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>8.5</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.58</v>
+        <v>2.82</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>4.45</v>
+        <v>6.65</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.95</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -909,10 +909,10 @@
         <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -921,13 +921,13 @@
         <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -939,7 +939,7 @@
         <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.81</v>
@@ -954,7 +954,7 @@
         <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF4" t="n">
         <v>2.1</v>
@@ -1019,19 +1019,19 @@
         <v>2.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
         <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.32</v>
@@ -1040,7 +1040,7 @@
         <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
         <v>1.44</v>
@@ -1058,13 +1058,13 @@
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC5" t="n">
         <v>2.69</v>
@@ -1079,7 +1079,7 @@
         <v>2.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
         <v>1.43</v>
@@ -1138,19 +1138,19 @@
         <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="R6" t="n">
         <v>1.7</v>
@@ -1159,37 +1159,37 @@
         <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
         <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
         <v>2.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
         <v>2.15</v>
@@ -1198,10 +1198,10 @@
         <v>1.61</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.43</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.32</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1257,31 +1257,31 @@
         <v>1.85</v>
       </c>
       <c r="M7" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
         <v>5.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
         <v>13</v>
@@ -1293,22 +1293,22 @@
         <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
         <v>2.48</v>
@@ -1320,7 +1320,7 @@
         <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
         <v>2.21</v>
       </c>
       <c r="O8" t="n">
-        <v>4.55</v>
+        <v>4.76</v>
       </c>
       <c r="P8" t="n">
         <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.63</v>
@@ -1403,31 +1403,31 @@
         <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
         <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
         <v>2.23</v>
@@ -1492,40 +1492,40 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
         <v>4.94</v>
       </c>
       <c r="N9" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="O9" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="U9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
@@ -1534,7 +1534,7 @@
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
         <v>1.62</v>
@@ -1543,22 +1543,22 @@
         <v>2.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46071.61458333334</v>
@@ -1736,7 +1736,7 @@
         <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
@@ -1748,34 +1748,34 @@
         <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
         <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AB11" t="n">
         <v>2.27</v>
@@ -1784,13 +1784,13 @@
         <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
         <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="AG11" t="n">
         <v>1.25</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
         <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>7.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.59</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>5.33</v>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
         <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2563,49 +2563,49 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
         <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
         <v>1.91</v>
@@ -2614,7 +2614,7 @@
         <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
         <v>1.3</v>
@@ -2626,10 +2626,10 @@
         <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>3.76</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.54</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>3.42</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="U20" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.16</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
         <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>9.18</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.58</v>
+        <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>4.45</v>
+        <v>6.75</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.09</v>
+        <v>3.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>9.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>2.82</v>
+        <v>3.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="V3" t="n">
-        <v>6.65</v>
+        <v>4.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>5.09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -915,7 +915,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
         <v>2.96</v>
@@ -930,7 +930,7 @@
         <v>6.75</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -942,13 +942,13 @@
         <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD4" t="n">
         <v>1.29</v>
@@ -1034,7 +1034,7 @@
         <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
         <v>2.96</v>
@@ -1058,16 +1058,16 @@
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
         <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.36</v>
@@ -1076,7 +1076,7 @@
         <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
         <v>1.23</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.94</v>
+        <v>5.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
         <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N7" t="n">
         <v>2.8</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.74</v>
+        <v>3.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE7" t="n">
         <v>2.15</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1379,16 +1379,16 @@
         <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.76</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
         <v>1.63</v>
@@ -1397,10 +1397,10 @@
         <v>2.13</v>
       </c>
       <c r="T8" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
         <v>8.9</v>
@@ -1412,28 +1412,28 @@
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
         <v>2.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
         <v>2.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
         <v>1.35</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>7.21</v>
       </c>
       <c r="M9" t="n">
-        <v>4.94</v>
+        <v>4.96</v>
       </c>
       <c r="N9" t="n">
         <v>1.39</v>
@@ -1504,28 +1504,28 @@
         <v>6.35</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q9" t="n">
         <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
         <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
@@ -1534,7 +1534,7 @@
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
         <v>1.62</v>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
         <v>2.5</v>
@@ -1641,7 +1641,7 @@
         <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
         <v>1.17</v>
@@ -1668,16 +1668,16 @@
         <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.12</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46071.625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N12" t="n">
         <v>1.8</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2090,19 +2090,19 @@
         <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
         <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
@@ -2126,7 +2126,7 @@
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
         <v>3.45</v>
@@ -2138,22 +2138,22 @@
         <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="R15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.39</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.81</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.45</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.72</v>
+        <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
         <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>1.83</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="M17" t="n">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="T17" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>4.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -2608,7 +2608,7 @@
         <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
         <v>1.85</v>
@@ -2620,13 +2620,13 @@
         <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
         <v>1.53</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="N19" t="n">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="O19" t="n">
-        <v>3.76</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2807,13 +2807,13 @@
         <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
         <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
         <v>2.43</v>
@@ -2822,10 +2822,10 @@
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
         <v>1.55</v>
@@ -2864,7 +2864,7 @@
         <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
         <v>1.29</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>9.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.82</v>
+        <v>3.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
-        <v>6.75</v>
+        <v>4.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>5.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.81</v>
+        <v>1.47</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>9.18</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.58</v>
+        <v>2.82</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>4.45</v>
+        <v>6.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.09</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,41 +1131,41 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>3.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.68</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
@@ -1174,34 +1174,34 @@
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="AB6" t="n">
         <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1284,13 +1284,13 @@
         <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
         <v>1.57</v>
@@ -1302,7 +1302,7 @@
         <v>2.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
         <v>5.75</v>
@@ -1317,10 +1317,10 @@
         <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,41 +1369,41 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O8" t="n">
         <v>2.75</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
@@ -1412,34 +1412,34 @@
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.21</v>
+        <v>7.4</v>
       </c>
       <c r="M9" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="N9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="O9" t="n">
         <v>6.35</v>
@@ -1513,7 +1513,7 @@
         <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.38</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.9</v>
-      </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O10" t="n">
         <v>4.33</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.22</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>3.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>5.33</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>3.08</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>3.52</v>
       </c>
       <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.33</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.33</v>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="O20" t="n">
-        <v>4.25</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.43</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>10.41</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>6.44</v>
       </c>
       <c r="N2" t="n">
         <v>1.19</v>
@@ -680,31 +680,31 @@
         <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
         <v>2.6</v>
@@ -713,13 +713,13 @@
         <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="n">
         <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
         <v>1.06</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P3" t="n">
         <v>2.15</v>
@@ -796,55 +796,55 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="T3" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AG3" t="n">
         <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -915,7 +915,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
         <v>2.96</v>
@@ -930,7 +930,7 @@
         <v>6.75</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -945,7 +945,7 @@
         <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC4" t="n">
         <v>3.04</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
         <v>2.5</v>
@@ -1058,16 +1058,16 @@
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA5" t="n">
         <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD5" t="n">
         <v>1.36</v>
@@ -1076,7 +1076,7 @@
         <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AG5" t="n">
         <v>1.23</v>
@@ -1617,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
         <v>4.33</v>
@@ -1626,7 +1626,7 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
         <v>4.2</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
         <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="P14" t="n">
         <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
         <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V14" t="n">
         <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
@@ -2129,13 +2129,13 @@
         <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
         <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC14" t="n">
         <v>3.16</v>
@@ -2150,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O15" t="n">
         <v>2.45</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.72</v>
+        <v>3.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
         <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2801,67 +2801,67 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="M20" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>8</v>
       </c>
       <c r="P20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.45</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.43</v>
       </c>
       <c r="U20" t="n">
         <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
         <v>1.15</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O7" t="n">
         <v>2.75</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.94</v>
+        <v>5.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
         <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
         <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N8" t="n">
         <v>2.8</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.33</v>
-      </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>3.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="AB8" t="n">
         <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.92</v>
+        <v>4.82</v>
       </c>
       <c r="N9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O9" t="n">
         <v>6.35</v>
@@ -1513,10 +1513,10 @@
         <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
         <v>1.57</v>
@@ -1531,7 +1531,7 @@
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
         <v>4.9</v>
@@ -1552,7 +1552,7 @@
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>3.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.42</v>
       </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.43</v>
-      </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.83</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.11</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
         <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.26</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.45</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF19" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>9.5</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
         <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>2.43</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V20" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AD20" t="n">
         <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10.41</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>9.18</v>
+        <v>3.32</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.02</v>
+        <v>3.42</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32</v>
+        <v>9.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.42</v>
+        <v>5.02</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,53 +1131,53 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.72</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
         <v>2.69</v>
@@ -1186,22 +1186,22 @@
         <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,53 +1369,53 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M8" t="n">
         <v>2.75</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.37</v>
-      </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AA8" t="n">
         <v>2.69</v>
@@ -1424,22 +1424,22 @@
         <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="N9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>6.35</v>
@@ -1513,7 +1513,7 @@
         <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.3</v>
@@ -1531,7 +1531,7 @@
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
         <v>4.9</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.2</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.83</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V14" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="M16" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.45</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.72</v>
+        <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.6</v>
+        <v>9.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>3.27</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>9.5</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>4.25</v>
       </c>
       <c r="P19" t="n">
         <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>2.43</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="W19" t="n">
         <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AD19" t="n">
         <v>1.46</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>4.25</v>
+        <v>3.08</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.43</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.42</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,53 +1131,53 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M6" t="n">
         <v>2.75</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.37</v>
-      </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AA6" t="n">
         <v>2.69</v>
@@ -1186,22 +1186,22 @@
         <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,53 +1369,53 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.5</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.72</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
         <v>2.69</v>
@@ -1424,22 +1424,22 @@
         <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1626,7 +1626,7 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -1674,7 +1674,7 @@
         <v>2.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
         <v>1.22</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.16</v>
+        <v>4.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.53</v>
-      </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="V15" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.27</v>
+        <v>3.66</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="W17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.11</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.26</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2685,10 +2685,10 @@
         <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
         <v>4.25</v>
@@ -2712,7 +2712,7 @@
         <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="W19" t="n">
         <v>1.11</v>
@@ -2745,7 +2745,7 @@
         <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
         <v>1.25</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.45</v>
+        <v>9.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>5.92</v>
       </c>
       <c r="N20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.8</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.32</v>
+        <v>8.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.42</v>
+        <v>5.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10.41</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>9.18</v>
+        <v>3.32</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.71</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.02</v>
+        <v>3.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -912,7 +912,7 @@
         <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -951,16 +951,16 @@
         <v>3.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
         <v>1.58</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
         <v>1.41</v>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
         <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
         <v>2.96</v>
@@ -1058,16 +1058,16 @@
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.36</v>
@@ -1079,7 +1079,7 @@
         <v>2.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
         <v>1.43</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="M6" t="n">
         <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O6" t="n">
         <v>4.33</v>
@@ -1153,7 +1153,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
         <v>2.13</v>
@@ -1165,7 +1165,7 @@
         <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
@@ -1180,28 +1180,28 @@
         <v>2.23</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
         <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AD6" t="n">
         <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
         <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N7" t="n">
         <v>2.8</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.33</v>
-      </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.8</v>
+        <v>3.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>5.93</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O8" t="n">
         <v>2.75</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.35</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.94</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1495,10 +1495,10 @@
         <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.85</v>
+        <v>4.83</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O9" t="n">
         <v>6.35</v>
@@ -1510,7 +1510,7 @@
         <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>3.5</v>
@@ -1549,7 +1549,7 @@
         <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
         <v>1.91</v>
@@ -1659,7 +1659,7 @@
         <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AC10" t="n">
         <v>2.25</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
@@ -1748,19 +1748,19 @@
         <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
@@ -1775,19 +1775,19 @@
         <v>4.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AD11" t="n">
         <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
         <v>2.25</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.45</v>
-      </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.3</v>
       </c>
-      <c r="V14" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.9</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="AA15" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.16</v>
+        <v>4.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
         <v>3.83</v>
@@ -2337,7 +2337,7 @@
         <v>2.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
@@ -2346,16 +2346,16 @@
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
         <v>3.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2367,7 +2367,7 @@
         <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="AA16" t="n">
         <v>2.1</v>
@@ -2379,7 +2379,7 @@
         <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
         <v>1.85</v>
@@ -2447,43 +2447,43 @@
         <v>4.6</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
         <v>5</v>
@@ -2492,10 +2492,10 @@
         <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
         <v>1.62</v>
@@ -2510,7 +2510,7 @@
         <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
         <v>3.08</v>
@@ -2596,7 +2596,7 @@
         <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
@@ -2623,7 +2623,7 @@
         <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
         <v>1.33</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="O19" t="n">
-        <v>4.25</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>9.65</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>5.92</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>2.43</v>
       </c>
       <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,41 +1131,41 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.53</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O6" t="n">
         <v>2.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
@@ -1174,34 +1174,34 @@
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,41 +1369,41 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>3.53</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.21</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
         <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
@@ -1412,34 +1412,34 @@
         <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="N9" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
         <v>6.35</v>
@@ -1531,10 +1531,10 @@
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
         <v>1.62</v>
@@ -1543,13 +1543,13 @@
         <v>2.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD9" t="n">
         <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
         <v>1.91</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>4.8</v>
+        <v>5.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
         <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2572,13 +2572,13 @@
         <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
         <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -2587,7 +2587,7 @@
         <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
         <v>1.44</v>
@@ -2620,10 +2620,10 @@
         <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
         <v>1.33</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>4.85</v>
       </c>
       <c r="W19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.1</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="O20" t="n">
-        <v>4.25</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="M2" t="n">
         <v>6.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O2" t="n">
-        <v>8.6</v>
+        <v>9.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
         <v>1.22</v>
@@ -683,7 +683,7 @@
         <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
         <v>1.62</v>
@@ -707,7 +707,7 @@
         <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AC2" t="n">
         <v>2.22</v>
@@ -796,13 +796,13 @@
         <v>3.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>2.74</v>
       </c>
       <c r="T3" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
         <v>1.37</v>
@@ -817,16 +817,16 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AC3" t="n">
         <v>3.05</v>
@@ -909,10 +909,10 @@
         <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -921,10 +921,10 @@
         <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
         <v>6.75</v>
@@ -939,13 +939,13 @@
         <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
         <v>3.04</v>
@@ -957,10 +957,10 @@
         <v>1.58</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
         <v>1.41</v>
@@ -1016,31 +1016,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="P5" t="n">
         <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
         <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="n">
         <v>1.44</v>
@@ -1061,28 +1061,28 @@
         <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB5" t="n">
         <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD5" t="n">
         <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46071.58333333334</v>
@@ -1144,22 +1144,22 @@
         <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="P6" t="n">
         <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="R6" t="n">
         <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="U6" t="n">
         <v>1.18</v>
@@ -1177,19 +1177,19 @@
         <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
         <v>2.48</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>4.76</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="T7" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="U7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AA7" t="n">
         <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.53</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AA8" t="n">
         <v>2.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>5.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1617,40 +1617,40 @@
         <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
         <v>5</v>
@@ -1659,25 +1659,25 @@
         <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46071.625</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M11" t="n">
         <v>3.95</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.85</v>
       </c>
       <c r="N11" t="n">
         <v>1.85</v>
@@ -1742,16 +1742,16 @@
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q11" t="n">
         <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
         <v>2.49</v>
@@ -1772,28 +1772,28 @@
         <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AB11" t="n">
         <v>2.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AD11" t="n">
         <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="n">
         <v>1.25</v>
@@ -2090,25 +2090,25 @@
         <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="T14" t="n">
         <v>2.99</v>
@@ -2123,7 +2123,7 @@
         <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
         <v>1.24</v>
@@ -2138,19 +2138,19 @@
         <v>1.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
         <v>1.58</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
-        <v>4.25</v>
+        <v>9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="R20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,41 +1131,41 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.69</v>
+        <v>4.76</v>
       </c>
       <c r="P6" t="n">
         <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.85</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
@@ -1174,34 +1174,34 @@
         <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>4.76</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AA7" t="n">
         <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="AD7" t="n">
         <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.96</v>
+        <v>5.85</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
         <v>9.300000000000001</v>
@@ -1409,37 +1409,37 @@
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.93</v>
+        <v>6.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
         <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1543,7 +1543,7 @@
         <v>2.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
         <v>1.44</v>
@@ -1552,7 +1552,7 @@
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
@@ -1730,43 +1730,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.17</v>
@@ -1775,13 +1775,13 @@
         <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="AD11" t="n">
         <v>1.48</v>
@@ -1793,7 +1793,7 @@
         <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
         <v>1.25</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>3.83</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="T15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.22</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.22</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.83</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>9</v>
+        <v>4.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T17" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>4.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.65</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="O20" t="n">
-        <v>4.25</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="U20" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>9.18</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.16</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.02</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32</v>
+        <v>8.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>1.61</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.42</v>
+        <v>4.99</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -909,10 +909,10 @@
         <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -954,7 +954,7 @@
         <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
         <v>2.1</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>2.77</v>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>2.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="T5" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AG5" t="n">
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46071.58333333334</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
         <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>4.76</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -1156,7 +1156,7 @@
         <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
         <v>3.76</v>
@@ -1165,16 +1165,16 @@
         <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
         <v>2.21</v>
@@ -1183,16 +1183,16 @@
         <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
         <v>6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
         <v>1.55</v>
@@ -1201,7 +1201,7 @@
         <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.96</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.93</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
         <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,34 +1373,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.87</v>
       </c>
       <c r="O8" t="n">
-        <v>2.69</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.85</v>
+        <v>3.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
         <v>9.300000000000001</v>
@@ -1409,37 +1409,37 @@
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1495,64 +1495,64 @@
         <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.84</v>
+        <v>4.87</v>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="O9" t="n">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
@@ -1611,67 +1611,67 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="N10" t="n">
         <v>1.73</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
         <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
         <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.39</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.42</v>
       </c>
       <c r="AG10" t="n">
         <v>1.22</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.4</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.22</v>
+        <v>4.22</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
         <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.72</v>
+        <v>3.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.22</v>
+        <v>3.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.7</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.42</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
         <v>2.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.75</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.21</v>
+        <v>2.52</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
-        <v>4.85</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
         <v>1.16</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2682,52 +2682,52 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
         <v>2.81</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="T19" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
         <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
         <v>1.85</v>
@@ -2736,19 +2736,19 @@
         <v>3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.29</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -671,22 +671,22 @@
         <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>3.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
         <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
         <v>7.3</v>
@@ -701,31 +701,31 @@
         <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
         <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
         <v>1.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="N3" t="n">
         <v>1.22</v>
@@ -790,22 +790,22 @@
         <v>8.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
         <v>4.5</v>
@@ -820,7 +820,7 @@
         <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="AA3" t="n">
         <v>1.44</v>
@@ -829,22 +829,22 @@
         <v>2.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
         <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="P4" t="n">
         <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
         <v>2.96</v>
@@ -936,13 +936,13 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
         <v>1.93</v>
@@ -951,19 +951,19 @@
         <v>3.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
         <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG4" t="n">
         <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46071.45833333334</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
         <v>3.25</v>
@@ -1025,13 +1025,13 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.86</v>
+        <v>3.54</v>
       </c>
       <c r="R5" t="n">
         <v>1.33</v>
@@ -1040,13 +1040,13 @@
         <v>2.91</v>
       </c>
       <c r="T5" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
@@ -1058,13 +1058,13 @@
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.86</v>
+        <v>4.03</v>
       </c>
       <c r="AA5" t="n">
         <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
         <v>2.7</v>
@@ -1076,7 +1076,7 @@
         <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AG5" t="n">
         <v>1.25</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O8" t="n">
         <v>2.5</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.8</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.96</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.34</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1620,13 +1620,13 @@
         <v>1.73</v>
       </c>
       <c r="O10" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
@@ -1635,49 +1635,49 @@
         <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="U10" t="n">
         <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="W10" t="n">
         <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
         <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46071.625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.95</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>3.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>1.84</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2090,19 +2090,19 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>2.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>4.57</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2111,13 +2111,13 @@
         <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
@@ -2129,10 +2129,10 @@
         <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
         <v>1.72</v>
@@ -2141,19 +2141,19 @@
         <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.72</v>
+        <v>3.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.36</v>
+        <v>2.72</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.52</v>
+        <v>4.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.54</v>
+        <v>2.42</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>2.81</v>
       </c>
       <c r="O17" t="n">
-        <v>4.71</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>3.22</v>
       </c>
       <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.25</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z17" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>4.54</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>4.71</v>
       </c>
       <c r="P18" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.42</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.81</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.22</v>
+        <v>2.43</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="U19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.44</v>
       </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="O20" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,38 +1131,38 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
         <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
         <v>13</v>
@@ -1171,37 +1171,37 @@
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,38 +1369,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
         <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
         <v>13</v>
@@ -1409,37 +1409,37 @@
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.87</v>
+        <v>4.92</v>
       </c>
       <c r="N9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="O9" t="n">
         <v>6.3</v>
@@ -1510,37 +1510,37 @@
         <v>1.89</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
         <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
         <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AC9" t="n">
         <v>2.63</v>
@@ -1552,7 +1552,7 @@
         <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.57</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>4.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>4.57</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.93</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.72</v>
+        <v>3.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.42</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.81</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>2.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.22</v>
+        <v>2.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="U17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.44</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2566,10 +2566,10 @@
         <v>4.54</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
         <v>4.71</v>
@@ -2578,52 +2578,52 @@
         <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="U18" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
         <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
         <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="n">
         <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AG18" t="n">
         <v>1.22</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O2" t="n">
-        <v>3.34</v>
+        <v>8.5</v>
       </c>
       <c r="P2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>8.5</v>
+        <v>3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>3.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
         <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AD7" t="n">
         <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,38 +1369,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
         <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
         <v>13</v>
@@ -1409,37 +1409,37 @@
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.87</v>
+        <v>1.94</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="T14" t="n">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.22</v>
+        <v>3.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.57</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>4.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.49</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.29</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.54</v>
+        <v>3.7</v>
       </c>
       <c r="M18" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O18" t="n">
-        <v>4.71</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.42</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>3.34</v>
+        <v>5.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>2.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.18</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>4.54</v>
       </c>
       <c r="M20" t="n">
-        <v>5.3</v>
+        <v>4.05</v>
       </c>
       <c r="N20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.27</v>
       </c>
-      <c r="O20" t="n">
-        <v>9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.4</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AC20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8.5</v>
+        <v>3.67</v>
       </c>
       <c r="P2" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.9</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>8.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -906,25 +906,25 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
         <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
         <v>6.75</v>
@@ -936,25 +936,25 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
         <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF4" t="n">
         <v>2.11</v>
@@ -963,7 +963,7 @@
         <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46071.45833333334</v>
@@ -1019,7 +1019,7 @@
         <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N5" t="n">
         <v>2.7</v>
@@ -1034,19 +1034,19 @@
         <v>3.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
         <v>2.91</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
@@ -1058,10 +1058,10 @@
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.03</v>
+        <v>3.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
         <v>2.05</v>
@@ -1076,7 +1076,7 @@
         <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AG5" t="n">
         <v>1.25</v>
@@ -1138,7 +1138,7 @@
         <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
         <v>2.87</v>
@@ -1153,37 +1153,37 @@
         <v>3.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
         <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
         <v>3.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
         <v>5.25</v>
@@ -1201,7 +1201,7 @@
         <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="M7" t="n">
         <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="O7" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,38 +1369,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
         <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>3.11</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
         <v>13</v>
@@ -1409,37 +1409,37 @@
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
       <c r="N9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="O9" t="n">
         <v>6.3</v>
@@ -1513,19 +1513,19 @@
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="T9" t="n">
         <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="M10" t="n">
         <v>4.05</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.97</v>
       </c>
       <c r="N10" t="n">
         <v>1.73</v>
@@ -1623,13 +1623,13 @@
         <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
         <v>3.58</v>
@@ -1638,10 +1638,10 @@
         <v>2.23</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>4.35</v>
       </c>
       <c r="W10" t="n">
         <v>1.12</v>
@@ -1653,13 +1653,13 @@
         <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.75</v>
+        <v>5.12</v>
       </c>
       <c r="AA10" t="n">
         <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AC10" t="n">
         <v>2.25</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N11" t="n">
         <v>1.8</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.95</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="M14" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>3.19</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="N15" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.22</v>
+        <v>3.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.93</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>4.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.42</v>
+        <v>4.54</v>
       </c>
       <c r="M17" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.72</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.66</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.18</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.04</v>
+        <v>2.31</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.7</v>
+        <v>11</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>3.96</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
         <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.84</v>
+        <v>2.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.54</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.73</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
-        <v>4.71</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.31</v>
+        <v>3.04</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O2" t="n">
-        <v>3.67</v>
+        <v>8.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.14</v>
+        <v>2.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10.56</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>6.53</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>8.5</v>
+        <v>3.67</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.17</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
         <v>3.12</v>
@@ -921,13 +921,13 @@
         <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -939,19 +939,19 @@
         <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="AA4" t="n">
         <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
         <v>2.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
         <v>1.63</v>
@@ -1031,7 +1031,7 @@
         <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.32</v>
@@ -1043,7 +1043,7 @@
         <v>2.53</v>
       </c>
       <c r="U5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
         <v>6.25</v>
@@ -1064,7 +1064,7 @@
         <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
         <v>2.7</v>
@@ -1082,7 +1082,7 @@
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46071.58333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
         <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>3.11</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T7" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="M8" t="n">
         <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.11</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1495,43 +1495,43 @@
         <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="N9" t="n">
         <v>1.42</v>
       </c>
       <c r="O9" t="n">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
         <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
         <v>5</v>
@@ -1540,16 +1540,16 @@
         <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
         <v>1.91</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.54</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.66</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.6</v>
       </c>
-      <c r="V17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AB17" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>2.64</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>4.54</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>4.3</v>
+        <v>4.66</v>
       </c>
       <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.49</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.72</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>2.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10.56</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>6.53</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>8.5</v>
+        <v>3.67</v>
       </c>
       <c r="P2" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>2.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.17</v>
+        <v>3.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>10.56</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>6.53</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>1.19</v>
       </c>
       <c r="O3" t="n">
-        <v>3.67</v>
+        <v>8.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.85</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>2.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>4.33</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.96</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,32 +1250,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.11</v>
+        <v>3.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="T7" t="n">
         <v>3.78</v>
@@ -1284,43 +1284,43 @@
         <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.74</v>
+        <v>3.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AD7" t="n">
         <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
         <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>3.11</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T8" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="U8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
         <v>1.8</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N14" t="n">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.95</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>4.54</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>4.66</v>
       </c>
       <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.49</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.54</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
-        <v>4.66</v>
+        <v>4.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z19" t="n">
         <v>4.4</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
-      </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -659,49 +659,49 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="M2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z2" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
@@ -710,16 +710,16 @@
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG2" t="n">
         <v>1.42</v>
@@ -778,70 +778,70 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10.56</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>6.53</v>
+        <v>5.88</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="O3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="P3" t="n">
         <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH3" t="n">
         <v>1.01</v>
@@ -897,40 +897,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M4" t="n">
         <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
         <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -942,7 +942,7 @@
         <v>3.66</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
         <v>1.95</v>
@@ -954,16 +954,16 @@
         <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
         <v>2.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46071.45833333334</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
         <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
         <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>6.25</v>
+        <v>6.95</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.86</v>
+        <v>3.42</v>
       </c>
       <c r="AA5" t="n">
         <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46071.58333333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.33</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="T6" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,32 +1250,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.96</v>
+        <v>3.11</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="T7" t="n">
         <v>3.78</v>
@@ -1284,43 +1284,43 @@
         <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.06</v>
+        <v>2.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AD7" t="n">
         <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="M8" t="n">
         <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.11</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1495,64 +1495,64 @@
         <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="N9" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
         <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AC9" t="n">
         <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.72</v>
+        <v>4.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="N16" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.22</v>
+        <v>3.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.54</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>4.66</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="T17" t="n">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.45</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.04</v>
+        <v>2.31</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>1.26</v>
       </c>
       <c r="O19" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.5</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.26</v>
+        <v>2.64</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
         <v>3.76</v>
@@ -683,13 +683,13 @@
         <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -701,13 +701,13 @@
         <v>1.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
         <v>3.5</v>
@@ -716,10 +716,10 @@
         <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG2" t="n">
         <v>1.42</v>
@@ -778,70 +778,70 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>5.88</v>
+        <v>5.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
         <v>7.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
         <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="U3" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AH3" t="n">
         <v>1.01</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M4" t="n">
         <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="P4" t="n">
         <v>2.16</v>
@@ -918,19 +918,19 @@
         <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
         <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -939,25 +939,25 @@
         <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
         <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
         <v>1.23</v>
@@ -1022,37 +1022,37 @@
         <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
         <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U5" t="n">
         <v>1.41</v>
       </c>
       <c r="V5" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.23</v>
@@ -1061,7 +1061,7 @@
         <v>3.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
         <v>1.85</v>
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="N9" t="n">
         <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
         <v>3.45</v>
@@ -1522,37 +1522,37 @@
         <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
         <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
         <v>1.61</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N11" t="n">
         <v>1.8</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46071.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="M14" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>3.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="T14" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="N15" t="n">
-        <v>3.19</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>4.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.32</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z17" t="n">
         <v>5</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O18" t="n">
         <v>4.4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.65</v>
       </c>
       <c r="P18" t="n">
         <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="U18" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
         <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
         <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.99</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11.5</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>1.26</v>
+        <v>2.62</v>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.63</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.64</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>2.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.1</v>
       </c>
       <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -662,7 +662,7 @@
         <v>2.77</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
         <v>2.3</v>
@@ -680,13 +680,13 @@
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
         <v>3.5</v>
@@ -722,10 +722,10 @@
         <v>1.89</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -778,37 +778,37 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M3" t="n">
         <v>5.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O3" t="n">
         <v>7.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="Q3" t="n">
         <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="W3" t="n">
         <v>1.09</v>
@@ -817,34 +817,34 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.08</v>
+        <v>3.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
         <v>2.4</v>
@@ -909,13 +909,13 @@
         <v>3.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
         <v>3.02</v>
@@ -930,7 +930,7 @@
         <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -945,13 +945,13 @@
         <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
         <v>3.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
         <v>1.64</v>
@@ -960,7 +960,7 @@
         <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AH4" t="n">
         <v>1.43</v>
@@ -1019,10 +1019,10 @@
         <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>2.8</v>
@@ -1040,10 +1040,10 @@
         <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
         <v>7.1</v>
@@ -1061,7 +1061,7 @@
         <v>3.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
         <v>1.85</v>
@@ -1073,10 +1073,10 @@
         <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AG5" t="n">
         <v>1.28</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,32 +1131,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.96</v>
+        <v>3.11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
         <v>3.78</v>
@@ -1165,43 +1165,43 @@
         <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.06</v>
+        <v>2.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,32 +1250,32 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.11</v>
+        <v>3.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="T7" t="n">
         <v>3.78</v>
@@ -1284,43 +1284,43 @@
         <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.74</v>
+        <v>3.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AD7" t="n">
         <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>7.43</v>
       </c>
       <c r="M9" t="n">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>6.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
@@ -1516,13 +1516,13 @@
         <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
@@ -1534,19 +1534,19 @@
         <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
         <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="n">
         <v>1.83</v>
@@ -1555,7 +1555,7 @@
         <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
         <v>1.05</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
         <v>1.8</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="N14" t="n">
-        <v>3.19</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.3</v>
+        <v>4.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.22</v>
+        <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.44</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.64</v>
+        <v>5.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>3.98</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.57</v>
+        <v>2.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.99</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.45</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.5</v>
+        <v>2.62</v>
       </c>
       <c r="M20" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.33</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>

--- a/jogos_2026-02-18.xlsx
+++ b/jogos_2026-02-18.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.77</v>
+        <v>8.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="O2" t="n">
-        <v>3.76</v>
+        <v>7.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.07</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>2.79</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.11</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.77</v>
+        <v>2.19</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>3.68</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46071.35416666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8.6</v>
+        <v>2.77</v>
       </c>
       <c r="M3" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>7.5</v>
+        <v>3.76</v>
       </c>
       <c r="P3" t="n">
-        <v>2.61</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>3.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>3.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE3" t="n">
-        <v>2.19</v>
+        <v>1.77</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.68</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46071.35416666666</v>
@@ -1138,7 +1138,7 @@
         <v>3.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
         <v>2.2</v>
@@ -1153,55 +1153,55 @@
         <v>3.11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
         <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
         <v>2.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
         <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="M7" t="n">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>2.71</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.96</v>
+        <v>5.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.84</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N8" t="n">
         <v>2.8</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.33</v>
-      </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>3.88</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="R8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.65</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AG8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.73</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46071.60416666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.29</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
         <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
         <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>4.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.12</v>
+        <v>5.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46071.625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.56</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46071.66666666666</v>
@@ -1983,13 +1983,13 @@
         <v>2.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="T13" t="n">
         <v>2.63</v>
@@ -1998,13 +1998,13 @@
         <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>1.24</v>
@@ -2013,28 +2013,28 @@
         <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
         <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46071.6875</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.22</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.19</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>4.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.83</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>4.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2.47</v>
       </c>
       <c r="O16" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46071.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="P17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.41</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.55</v>
+        <v>3.98</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>11.5</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.33</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46071.70833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.4</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.84</v>
-      </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>5.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46071.70833333334</v>
